--- a/.cursor/_olds/info/bom_test.xlsx
+++ b/.cursor/_olds/info/bom_test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documents\PROJECTS\prod-scheduler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\_PROJECTS\MES_midex\.cursor\_olds\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402AB536-CF2D-43EE-93D3-9277DA9A2B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3263E8C6-C1F7-4A32-B3E2-5CD95BAEDFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="21429" xr2:uid="{39057C33-F26F-46A8-A6DF-CA4564F601AF}"/>
   </bookViews>
@@ -512,9 +512,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -860,16 +861,17 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>0.02</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F2" t="s">
@@ -877,16 +879,17 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F3" t="s">
@@ -894,19 +897,19 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>12.4</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F4" t="s">
@@ -914,19 +917,19 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>2.7777777777777801E-2</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>43.95</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
@@ -934,16 +937,17 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>0.192</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
@@ -951,19 +955,19 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>29.5</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F7" t="s">
@@ -971,19 +975,19 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>190</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
@@ -991,19 +995,19 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>0.08</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>228.59</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F9" t="s">
@@ -1011,16 +1015,17 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
@@ -1028,19 +1033,19 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>0.1</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>90</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F11" t="s">
@@ -1048,19 +1053,19 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>22</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
@@ -1068,19 +1073,19 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>285</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
@@ -1088,19 +1093,19 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>491.59</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
@@ -1108,19 +1113,19 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>0.03</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>197.2</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F15" t="s">
@@ -1128,19 +1133,19 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>1E-3</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>2295</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
@@ -1148,19 +1153,19 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>0.02</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>285</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F17" t="s">
